--- a/data/trans_orig/Q17B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q17B-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de veces que ha consultado al médico en las 2 últimas semanas</t>
+          <t>Número medio de veces que la población ha tenido una consulta médica en las 2 últimas semanas (tasa de respuesta: 99,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,17; 0,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,4</t>
+          <t>0,29; 0,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,28</t>
+          <t>0,18; 0,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,41</t>
+          <t>0,31; 0,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,34</t>
+          <t>0,27; 0,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,32</t>
+          <t>0,25; 0,31</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -861,17 +861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,35</t>
+          <t>0,26; 0,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,46</t>
+          <t>0,32; 0,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,25</t>
+          <t>0,09; 0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,48</t>
+          <t>0,38; 0,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,55</t>
+          <t>0,4; 0,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,39</t>
+          <t>0,33; 0,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,27</t>
+          <t>0,15; 0,27</t>
         </is>
       </c>
     </row>
@@ -1006,22 +1006,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,3</t>
+          <t>0,21; 0,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,33</t>
+          <t>0,2; 0,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,39</t>
+          <t>0,3; 0,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,41</t>
+          <t>0,31; 0,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,27</t>
+          <t>0,1; 0,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,36</t>
+          <t>0,28; 0,35</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,33</t>
+          <t>0,24; 0,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,52</t>
+          <t>0,38; 0,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,56</t>
+          <t>0,39; 0,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,4</t>
+          <t>0,31; 0,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,37</t>
+          <t>0,29; 0,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,45</t>
+          <t>0,33; 0,44</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,27</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,46</t>
+          <t>0,39; 0,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">

--- a/data/trans_orig/Q17B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q17B-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -721,42 +721,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,41</t>
+          <t>0,28; 0,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,39</t>
+          <t>0,29; 0,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,27</t>
+          <t>0,17; 0,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,42</t>
+          <t>0,31; 0,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,5</t>
+          <t>0,39; 0,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,6</t>
+          <t>0,43; 0,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,35</t>
+          <t>0,27; 0,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,31</t>
+          <t>0,25; 0,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,47</t>
+          <t>0,38; 0,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,3</t>
+          <t>0,23; 0,29</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,26</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,28</t>
+          <t>0,2; 0,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,34</t>
+          <t>0,25; 0,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,25</t>
+          <t>0,2; 0,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,47</t>
+          <t>0,39; 0,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,4</t>
+          <t>0,33; 0,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,27</t>
+          <t>0,23; 0,29</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -1001,22 +1001,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,34</t>
+          <t>0,24; 0,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,3</t>
+          <t>0,22; 0,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,32</t>
+          <t>0,19; 0,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,4</t>
+          <t>0,3; 0,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,43</t>
+          <t>0,33; 0,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,27</t>
+          <t>0,26; 0,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>0,29; 0,35</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>0,28; 0,35</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 0,35</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,27</t>
+          <t>0,24; 0,31</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,35</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,31</t>
+          <t>0,22; 0,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,46</t>
+          <t>0,35; 0,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,51</t>
+          <t>0,38; 0,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,55</t>
+          <t>0,37; 0,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,36</t>
+          <t>0,3; 0,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,44</t>
+          <t>0,32; 0,39</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,14 +1243,14 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>0,31</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0,35</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,35</t>
+          <t>0,3; 0,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,39; 0,44</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>0,39; 0,45</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,39; 0,45</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,35</t>
+          <t>0,31; 0,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,3</t>
+          <t>0,27; 0,3</t>
         </is>
       </c>
     </row>
